--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>61.27949</v>
+      </c>
+      <c r="C2">
+        <v>95.27216</v>
+      </c>
+      <c r="D2">
+        <v>86.31399999999999</v>
+      </c>
+      <c r="E2">
+        <v>47.36071</v>
+      </c>
+      <c r="F2">
         <v>61.59446</v>
       </c>
-      <c r="C2">
-        <v>61.27949</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>99.29794</v>
       </c>
-      <c r="E2">
-        <v>95.27216</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>107.2474</v>
       </c>
-      <c r="G2">
-        <v>86.31399999999999</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>68.86816</v>
-      </c>
-      <c r="I2">
-        <v>47.36071</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>64.6049</v>
+      </c>
+      <c r="C3">
+        <v>97.16784</v>
+      </c>
+      <c r="D3">
+        <v>82.72920999999999</v>
+      </c>
+      <c r="E3">
+        <v>33.58708</v>
+      </c>
+      <c r="F3">
         <v>64.7139</v>
       </c>
-      <c r="C3">
-        <v>64.6049</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>102.8322</v>
       </c>
-      <c r="E3">
-        <v>97.16784</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>103.0917</v>
       </c>
-      <c r="G3">
-        <v>82.72920999999999</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>47.0479</v>
-      </c>
-      <c r="I3">
-        <v>33.58708</v>
       </c>
     </row>
     <row r="4">
@@ -473,25 +473,25 @@
         <v>61.82573</v>
       </c>
       <c r="C4">
+        <v>96.80365</v>
+      </c>
+      <c r="D4">
+        <v>89.32462</v>
+      </c>
+      <c r="E4">
+        <v>41.21547</v>
+      </c>
+      <c r="F4">
         <v>61.82573</v>
       </c>
-      <c r="D4">
+      <c r="G4">
         <v>100.1142</v>
       </c>
-      <c r="E4">
-        <v>96.80365</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>103.7037</v>
       </c>
-      <c r="G4">
-        <v>89.32462</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>52.37569</v>
-      </c>
-      <c r="I4">
-        <v>41.21547</v>
       </c>
     </row>
     <row r="5">
@@ -504,25 +504,25 @@
         <v>70.91634000000001</v>
       </c>
       <c r="C5">
+        <v>99.13420000000001</v>
+      </c>
+      <c r="D5">
+        <v>83.80567000000001</v>
+      </c>
+      <c r="E5">
+        <v>34.54546</v>
+      </c>
+      <c r="F5">
         <v>70.91634000000001</v>
       </c>
-      <c r="D5">
+      <c r="G5">
         <v>104.1126</v>
       </c>
-      <c r="E5">
-        <v>99.13420000000001</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>93.11741000000001</v>
       </c>
-      <c r="G5">
-        <v>83.80567000000001</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>43.11688</v>
-      </c>
-      <c r="I5">
-        <v>34.54546</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>63.63838</v>
+      </c>
+      <c r="C6">
+        <v>96.23882999999999</v>
+      </c>
+      <c r="D6">
+        <v>87.76635</v>
+      </c>
+      <c r="E6">
+        <v>39.63621</v>
+      </c>
+      <c r="F6">
         <v>63.77133</v>
       </c>
-      <c r="C6">
-        <v>63.63838</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>99.49401</v>
       </c>
-      <c r="E6">
-        <v>96.23882999999999</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>105.327</v>
       </c>
-      <c r="G6">
-        <v>87.76635</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>59.83503</v>
-      </c>
-      <c r="I6">
-        <v>39.63621</v>
       </c>
     </row>
     <row r="7">
@@ -566,25 +566,25 @@
         <v>67.03125</v>
       </c>
       <c r="C7">
+        <v>97.70992</v>
+      </c>
+      <c r="D7">
+        <v>88.60465000000001</v>
+      </c>
+      <c r="E7">
+        <v>37.28814</v>
+      </c>
+      <c r="F7">
         <v>67.03125</v>
       </c>
-      <c r="D7">
+      <c r="G7">
         <v>104.0349</v>
       </c>
-      <c r="E7">
-        <v>97.70992</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>114.186</v>
       </c>
-      <c r="G7">
-        <v>88.60465000000001</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>51.04686</v>
-      </c>
-      <c r="I7">
-        <v>37.28814</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>65.82031000000001</v>
+      </c>
+      <c r="C8">
+        <v>95.5414</v>
+      </c>
+      <c r="D8">
+        <v>85.80931</v>
+      </c>
+      <c r="E8">
+        <v>36.79333</v>
+      </c>
+      <c r="F8">
         <v>66.01563</v>
       </c>
-      <c r="C8">
-        <v>65.82031000000001</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>100</v>
       </c>
-      <c r="E8">
-        <v>95.5414</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>106.6519</v>
       </c>
-      <c r="G8">
-        <v>85.80931</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>49.67562</v>
-      </c>
-      <c r="I8">
-        <v>36.79333</v>
       </c>
     </row>
     <row r="9">
@@ -628,25 +628,25 @@
         <v>61.70886</v>
       </c>
       <c r="C9">
+        <v>96.41407</v>
+      </c>
+      <c r="D9">
+        <v>80.44383000000001</v>
+      </c>
+      <c r="E9">
+        <v>32.84621</v>
+      </c>
+      <c r="F9">
         <v>61.70886</v>
       </c>
-      <c r="D9">
+      <c r="G9">
         <v>102.3681</v>
       </c>
-      <c r="E9">
-        <v>96.41407</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>93.61997</v>
       </c>
-      <c r="G9">
-        <v>80.44383000000001</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>44.25887</v>
-      </c>
-      <c r="I9">
-        <v>32.84621</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>62.83328</v>
+      </c>
+      <c r="C10">
+        <v>96.98222</v>
+      </c>
+      <c r="D10">
+        <v>85.10029</v>
+      </c>
+      <c r="E10">
+        <v>34.85144</v>
+      </c>
+      <c r="F10">
         <v>62.8654</v>
       </c>
-      <c r="C10">
-        <v>62.83328</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>100.9715</v>
       </c>
-      <c r="E10">
-        <v>96.98222</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>102.456</v>
       </c>
-      <c r="G10">
-        <v>85.10029</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>48.86142</v>
-      </c>
-      <c r="I10">
-        <v>34.85144</v>
       </c>
     </row>
     <row r="11">
@@ -690,25 +690,25 @@
         <v>60.22032</v>
       </c>
       <c r="C11">
+        <v>97.54861</v>
+      </c>
+      <c r="D11">
+        <v>82.96042</v>
+      </c>
+      <c r="E11">
+        <v>37.08134</v>
+      </c>
+      <c r="F11">
         <v>60.22032</v>
       </c>
-      <c r="D11">
+      <c r="G11">
         <v>103.973</v>
       </c>
-      <c r="E11">
-        <v>97.54861</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>98.45094</v>
       </c>
-      <c r="G11">
-        <v>82.96042</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>52.07336</v>
-      </c>
-      <c r="I11">
-        <v>37.08134</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>62.37149</v>
+      </c>
+      <c r="C12">
+        <v>96.48727</v>
+      </c>
+      <c r="D12">
+        <v>84.39951000000001</v>
+      </c>
+      <c r="E12">
+        <v>39.1553</v>
+      </c>
+      <c r="F12">
         <v>62.71419</v>
       </c>
-      <c r="C12">
-        <v>62.37149</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>100.6305</v>
       </c>
-      <c r="E12">
-        <v>96.48727</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>103.962</v>
       </c>
-      <c r="G12">
-        <v>84.39951000000001</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>57.32512</v>
-      </c>
-      <c r="I12">
-        <v>39.1553</v>
       </c>
     </row>
     <row r="13">
@@ -752,25 +752,25 @@
         <v>61.48282</v>
       </c>
       <c r="C13">
+        <v>97.2253</v>
+      </c>
+      <c r="D13">
+        <v>84.41558999999999</v>
+      </c>
+      <c r="E13">
+        <v>33.83948</v>
+      </c>
+      <c r="F13">
         <v>61.48282</v>
       </c>
-      <c r="D13">
+      <c r="G13">
         <v>102.3307</v>
       </c>
-      <c r="E13">
-        <v>97.2253</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>99.5671</v>
       </c>
-      <c r="G13">
-        <v>84.41558999999999</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>45.01085</v>
-      </c>
-      <c r="I13">
-        <v>33.83948</v>
       </c>
     </row>
     <row r="14">
@@ -783,25 +783,25 @@
         <v>64.80768999999999</v>
       </c>
       <c r="C14">
+        <v>96.69749</v>
+      </c>
+      <c r="D14">
+        <v>83.17534999999999</v>
+      </c>
+      <c r="E14">
+        <v>40.64436</v>
+      </c>
+      <c r="F14">
         <v>64.80768999999999</v>
       </c>
-      <c r="D14">
+      <c r="G14">
         <v>100.9247</v>
       </c>
-      <c r="E14">
-        <v>96.69749</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>92.65403000000001</v>
       </c>
-      <c r="G14">
-        <v>83.17534999999999</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>54.15118</v>
-      </c>
-      <c r="I14">
-        <v>40.64436</v>
       </c>
     </row>
     <row r="15">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>63.85037</v>
+      </c>
+      <c r="C15">
+        <v>95.92341</v>
+      </c>
+      <c r="D15">
+        <v>84.96841000000001</v>
+      </c>
+      <c r="E15">
+        <v>40.56966</v>
+      </c>
+      <c r="F15">
         <v>64.06934</v>
       </c>
-      <c r="C15">
-        <v>63.85037</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>101.9269</v>
       </c>
-      <c r="E15">
-        <v>95.92341</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>105.9721</v>
       </c>
-      <c r="G15">
-        <v>84.96841000000001</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>58.64399</v>
-      </c>
-      <c r="I15">
-        <v>40.56966</v>
       </c>
     </row>
     <row r="16">
@@ -845,25 +845,25 @@
         <v>69.3356</v>
       </c>
       <c r="C16">
+        <v>97.84836</v>
+      </c>
+      <c r="D16">
+        <v>86.7589</v>
+      </c>
+      <c r="E16">
+        <v>44.40228</v>
+      </c>
+      <c r="F16">
         <v>69.3356</v>
       </c>
-      <c r="D16">
+      <c r="G16">
         <v>101.1271</v>
       </c>
-      <c r="E16">
-        <v>97.84836</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>97.2332</v>
       </c>
-      <c r="G16">
-        <v>86.7589</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>58.72865</v>
-      </c>
-      <c r="I16">
-        <v>44.40228</v>
       </c>
     </row>
     <row r="17">
@@ -876,25 +876,25 @@
         <v>74.20923999999999</v>
       </c>
       <c r="C17">
+        <v>97.53623</v>
+      </c>
+      <c r="D17">
+        <v>87.83069</v>
+      </c>
+      <c r="E17">
+        <v>47.16157</v>
+      </c>
+      <c r="F17">
         <v>74.20923999999999</v>
       </c>
-      <c r="D17">
+      <c r="G17">
         <v>101.3043</v>
       </c>
-      <c r="E17">
-        <v>97.53623</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>99.73545</v>
       </c>
-      <c r="G17">
-        <v>87.83069</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>59.53421</v>
-      </c>
-      <c r="I17">
-        <v>47.16157</v>
       </c>
     </row>
     <row r="18">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>65.71693999999999</v>
+      </c>
+      <c r="C18">
+        <v>95.10339</v>
+      </c>
+      <c r="D18">
+        <v>84.83280000000001</v>
+      </c>
+      <c r="E18">
+        <v>35.40221</v>
+      </c>
+      <c r="F18">
         <v>65.90276</v>
       </c>
-      <c r="C18">
-        <v>65.71693999999999</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>99.33672</v>
       </c>
-      <c r="E18">
-        <v>95.10339</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>102.3487</v>
       </c>
-      <c r="G18">
-        <v>84.83280000000001</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>50.69416</v>
-      </c>
-      <c r="I18">
-        <v>35.40221</v>
       </c>
     </row>
     <row r="19">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>69</v>
+      </c>
+      <c r="C19">
+        <v>96.86660999999999</v>
+      </c>
+      <c r="D19">
+        <v>83.44710000000001</v>
+      </c>
+      <c r="E19">
+        <v>33.58925</v>
+      </c>
+      <c r="F19">
         <v>69.14286</v>
       </c>
-      <c r="C19">
-        <v>69</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>100.6267</v>
       </c>
-      <c r="E19">
-        <v>96.86660999999999</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>96.58703</v>
       </c>
-      <c r="G19">
-        <v>83.44710000000001</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>45.58541</v>
-      </c>
-      <c r="I19">
-        <v>33.58925</v>
       </c>
     </row>
     <row r="20">
@@ -966,28 +966,28 @@
         </is>
       </c>
       <c r="B20">
+        <v>70.08620000000001</v>
+      </c>
+      <c r="C20">
+        <v>96.44468999999999</v>
+      </c>
+      <c r="D20">
+        <v>86.9258</v>
+      </c>
+      <c r="E20">
+        <v>41.31206</v>
+      </c>
+      <c r="F20">
         <v>70.34483</v>
       </c>
-      <c r="C20">
-        <v>70.08620000000001</v>
-      </c>
-      <c r="D20">
+      <c r="G20">
         <v>99.71783000000001</v>
       </c>
-      <c r="E20">
-        <v>96.44468999999999</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>104.2403</v>
       </c>
-      <c r="G20">
-        <v>86.9258</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>57.1513</v>
-      </c>
-      <c r="I20">
-        <v>41.31206</v>
       </c>
     </row>
     <row r="21">
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="B21">
+        <v>70.16623</v>
+      </c>
+      <c r="C21">
+        <v>96.74930999999999</v>
+      </c>
+      <c r="D21">
+        <v>88.68313000000001</v>
+      </c>
+      <c r="E21">
+        <v>39.63049</v>
+      </c>
+      <c r="F21">
         <v>70.25372</v>
       </c>
-      <c r="C21">
-        <v>70.16623</v>
-      </c>
-      <c r="D21">
+      <c r="G21">
         <v>99.61433</v>
       </c>
-      <c r="E21">
-        <v>96.74930999999999</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>101.6461</v>
       </c>
-      <c r="G21">
-        <v>88.68313000000001</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>49.74596</v>
-      </c>
-      <c r="I21">
-        <v>39.63049</v>
       </c>
     </row>
     <row r="22">
@@ -1028,28 +1028,28 @@
         </is>
       </c>
       <c r="B22">
+        <v>60.36086</v>
+      </c>
+      <c r="C22">
+        <v>96.64879999999999</v>
+      </c>
+      <c r="D22">
+        <v>86.30759</v>
+      </c>
+      <c r="E22">
+        <v>35.48494</v>
+      </c>
+      <c r="F22">
         <v>60.52488</v>
       </c>
-      <c r="C22">
-        <v>60.36086</v>
-      </c>
-      <c r="D22">
+      <c r="G22">
         <v>100.9718</v>
       </c>
-      <c r="E22">
-        <v>96.64879999999999</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>100.8436</v>
       </c>
-      <c r="G22">
-        <v>86.30759</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>49.65243</v>
-      </c>
-      <c r="I22">
-        <v>35.48494</v>
       </c>
     </row>
     <row r="23">
@@ -1062,25 +1062,25 @@
         <v>63.18182</v>
       </c>
       <c r="C23">
+        <v>96.33252</v>
+      </c>
+      <c r="D23">
+        <v>85.18519000000001</v>
+      </c>
+      <c r="E23">
+        <v>52.11581</v>
+      </c>
+      <c r="F23">
         <v>63.18182</v>
       </c>
-      <c r="D23">
+      <c r="G23">
         <v>102.6895</v>
       </c>
-      <c r="E23">
-        <v>96.33252</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>98.14815</v>
       </c>
-      <c r="G23">
-        <v>85.18519000000001</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>62.80624</v>
-      </c>
-      <c r="I23">
-        <v>52.11581</v>
       </c>
     </row>
     <row r="24">
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="B24">
+        <v>71.15128</v>
+      </c>
+      <c r="C24">
+        <v>97.0359</v>
+      </c>
+      <c r="D24">
+        <v>83.68101</v>
+      </c>
+      <c r="E24">
+        <v>43.03141</v>
+      </c>
+      <c r="F24">
         <v>71.38835</v>
       </c>
-      <c r="C24">
-        <v>71.15128</v>
-      </c>
-      <c r="D24">
+      <c r="G24">
         <v>102.5022</v>
       </c>
-      <c r="E24">
-        <v>97.0359</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>109.5994</v>
       </c>
-      <c r="G24">
-        <v>83.68101</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>65.73815999999999</v>
-      </c>
-      <c r="I24">
-        <v>43.03141</v>
       </c>
     </row>
     <row r="25">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="B25">
+        <v>63.98417</v>
+      </c>
+      <c r="C25">
+        <v>95.97602999999999</v>
+      </c>
+      <c r="D25">
+        <v>82.09981999999999</v>
+      </c>
+      <c r="E25">
+        <v>34.73054</v>
+      </c>
+      <c r="F25">
         <v>64.1161</v>
       </c>
-      <c r="C25">
-        <v>63.98417</v>
-      </c>
-      <c r="D25">
+      <c r="G25">
         <v>101.0274</v>
       </c>
-      <c r="E25">
-        <v>95.97602999999999</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>104.6472</v>
       </c>
-      <c r="G25">
-        <v>82.09981999999999</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>49.79272</v>
-      </c>
-      <c r="I25">
-        <v>34.73054</v>
       </c>
     </row>
     <row r="26">
@@ -1152,28 +1152,28 @@
         </is>
       </c>
       <c r="B26">
+        <v>64.53306000000001</v>
+      </c>
+      <c r="C26">
+        <v>96.79358999999999</v>
+      </c>
+      <c r="D26">
+        <v>84.23676</v>
+      </c>
+      <c r="E26">
+        <v>30.3081</v>
+      </c>
+      <c r="F26">
         <v>64.58552</v>
       </c>
-      <c r="C26">
-        <v>64.53306000000001</v>
-      </c>
-      <c r="D26">
+      <c r="G26">
         <v>102.004</v>
       </c>
-      <c r="E26">
-        <v>96.79358999999999</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>102.8037</v>
       </c>
-      <c r="G26">
-        <v>84.23676</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>41.96249</v>
-      </c>
-      <c r="I26">
-        <v>30.3081</v>
       </c>
     </row>
     <row r="27">
@@ -1183,28 +1183,28 @@
         </is>
       </c>
       <c r="B27">
+        <v>64.76533999999999</v>
+      </c>
+      <c r="C27">
+        <v>96.61166</v>
+      </c>
+      <c r="D27">
+        <v>82.28314</v>
+      </c>
+      <c r="E27">
+        <v>39.17091</v>
+      </c>
+      <c r="F27">
         <v>64.80145</v>
       </c>
-      <c r="C27">
-        <v>64.76533999999999</v>
-      </c>
-      <c r="D27">
+      <c r="G27">
         <v>101.5622</v>
       </c>
-      <c r="E27">
-        <v>96.61166</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>103.1097</v>
       </c>
-      <c r="G27">
-        <v>82.28314</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>51.58501</v>
-      </c>
-      <c r="I27">
-        <v>39.17091</v>
       </c>
     </row>
     <row r="28">
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="B28">
+        <v>63.48148</v>
+      </c>
+      <c r="C28">
+        <v>96.72969000000001</v>
+      </c>
+      <c r="D28">
+        <v>83.96664</v>
+      </c>
+      <c r="E28">
+        <v>31.27615</v>
+      </c>
+      <c r="F28">
         <v>63.55556</v>
       </c>
-      <c r="C28">
-        <v>63.48148</v>
-      </c>
-      <c r="D28">
+      <c r="G28">
         <v>102.1461</v>
       </c>
-      <c r="E28">
-        <v>96.72969000000001</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>101.3902</v>
       </c>
-      <c r="G28">
-        <v>83.96664</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>41.10879</v>
-      </c>
-      <c r="I28">
-        <v>31.27615</v>
       </c>
     </row>
     <row r="29">
@@ -1245,28 +1245,28 @@
         </is>
       </c>
       <c r="B29">
+        <v>63.47032</v>
+      </c>
+      <c r="C29">
+        <v>95.86443</v>
+      </c>
+      <c r="D29">
+        <v>83.41500000000001</v>
+      </c>
+      <c r="E29">
+        <v>38.8597</v>
+      </c>
+      <c r="F29">
         <v>63.60078</v>
       </c>
-      <c r="C29">
-        <v>63.47032</v>
-      </c>
-      <c r="D29">
+      <c r="G29">
         <v>101.9367</v>
       </c>
-      <c r="E29">
-        <v>95.86443</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>104.6363</v>
       </c>
-      <c r="G29">
-        <v>83.41500000000001</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>51.97509</v>
-      </c>
-      <c r="I29">
-        <v>38.8597</v>
       </c>
     </row>
     <row r="30">
@@ -1279,25 +1279,25 @@
         <v>68.08712</v>
       </c>
       <c r="C30">
+        <v>96.99681</v>
+      </c>
+      <c r="D30">
+        <v>82.68591000000001</v>
+      </c>
+      <c r="E30">
+        <v>34.84252</v>
+      </c>
+      <c r="F30">
         <v>68.08712</v>
       </c>
-      <c r="D30">
+      <c r="G30">
         <v>103.4505</v>
       </c>
-      <c r="E30">
-        <v>96.99681</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>97.44728000000001</v>
       </c>
-      <c r="G30">
-        <v>82.68591000000001</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>50.91864</v>
-      </c>
-      <c r="I30">
-        <v>34.84252</v>
       </c>
     </row>
     <row r="31">
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="B31">
+        <v>63.21202</v>
+      </c>
+      <c r="C31">
+        <v>96.92695000000001</v>
+      </c>
+      <c r="D31">
+        <v>82.19047999999999</v>
+      </c>
+      <c r="E31">
+        <v>30.89207</v>
+      </c>
+      <c r="F31">
         <v>63.37025</v>
       </c>
-      <c r="C31">
-        <v>63.21202</v>
-      </c>
-      <c r="D31">
+      <c r="G31">
         <v>103.5265</v>
       </c>
-      <c r="E31">
-        <v>96.92695000000001</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>104.7619</v>
       </c>
-      <c r="G31">
-        <v>82.19047999999999</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>44.21806</v>
-      </c>
-      <c r="I31">
-        <v>30.89207</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:48</t>
+    <t xml:space="preserve">2026-08-02 19:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:43</t>
+    <t xml:space="preserve">2026-08-05 10:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:36</t>
+    <t xml:space="preserve">2026-08-16 09:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:48</t>
+    <t xml:space="preserve">2026-08-19 12:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:01</t>
+    <t xml:space="preserve">2026-08-28 11:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2019_maule.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:27</t>
+    <t xml:space="preserve">2026-09-06 17:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
